--- a/artfynd/A 21038-2025 artfynd.xlsx
+++ b/artfynd/A 21038-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89124622</v>
+        <v>89124625</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533839.9527199565</v>
+        <v>533895</v>
       </c>
       <c r="R2" t="n">
-        <v>6906067.831782358</v>
+        <v>6906079</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89124621</v>
+        <v>89124618</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533836.1113725287</v>
+        <v>533817</v>
       </c>
       <c r="R3" t="n">
-        <v>6906078.96429588</v>
+        <v>6906121</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +844,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89124625</v>
+        <v>89124620</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533894.8444134238</v>
+        <v>533833</v>
       </c>
       <c r="R4" t="n">
-        <v>6906079.091143919</v>
+        <v>6906085</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,19 +945,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89124624</v>
+        <v>89124623</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533893.9451008886</v>
+        <v>533867</v>
       </c>
       <c r="R5" t="n">
-        <v>6906075.823796462</v>
+        <v>6906055</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,19 +1046,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89124626</v>
+        <v>89124627</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533892.8297014839</v>
+        <v>533899</v>
       </c>
       <c r="R6" t="n">
-        <v>6906093.965718396</v>
+        <v>6906096</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,19 +1147,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89124620</v>
+        <v>89124626</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533832.7877273862</v>
+        <v>533893</v>
       </c>
       <c r="R7" t="n">
-        <v>6906084.981870806</v>
+        <v>6906094</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,19 +1248,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89124618</v>
+        <v>89124622</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533817.0409338177</v>
+        <v>533840</v>
       </c>
       <c r="R8" t="n">
-        <v>6906121.129402314</v>
+        <v>6906068</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1444,19 +1349,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89124623</v>
+        <v>89124621</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533867.1179217109</v>
+        <v>533836</v>
       </c>
       <c r="R9" t="n">
-        <v>6906055.072501997</v>
+        <v>6906079</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1560,19 +1450,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89124627</v>
+        <v>89124624</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533898.870155225</v>
+        <v>533894</v>
       </c>
       <c r="R10" t="n">
-        <v>6906095.888549658</v>
+        <v>6906076</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1676,19 +1551,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 21038-2025 artfynd.xlsx
+++ b/artfynd/A 21038-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124625</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124618</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124623</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124627</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124626</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124622</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124621</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,8 +1626,24 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>